--- a/grupos/5ASV - Estadisticos 20241.xlsx
+++ b/grupos/5ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -170,12 +170,12 @@
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
@@ -191,64 +191,28 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
+    <t>COLOHUA</t>
   </si>
   <si>
     <t>ELIZALDE</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>CELINA MONSERRAT</t>
+    <t>MIA NOEMI</t>
   </si>
   <si>
     <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MARCELO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
   </si>
   <si>
     <t>AZUL MARIAM</t>
@@ -759,22 +723,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -807,10 +771,10 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -836,22 +800,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -872,19 +836,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -916,19 +880,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -952,16 +916,16 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -990,22 +954,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1032,16 +996,16 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1067,22 +1031,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1109,16 +1073,16 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1144,22 +1108,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1180,7 +1144,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1192,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1221,22 +1185,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1257,19 +1221,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1298,22 +1262,22 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1340,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1349,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1375,22 +1339,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1411,19 +1375,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1452,22 +1416,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1488,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1500,7 +1464,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1529,22 +1493,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1571,13 +1535,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1606,22 +1570,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1642,7 +1606,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1654,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1683,22 +1647,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1719,19 +1683,19 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1760,22 +1724,22 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1796,10 +1760,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1808,10 +1772,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1837,22 +1801,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1879,13 +1843,13 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1914,22 +1878,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1956,16 +1920,16 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1991,22 +1955,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2027,19 +1991,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2068,22 +2032,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2107,7 +2071,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2116,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2145,22 +2109,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2181,19 +2145,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2222,22 +2186,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2258,22 +2222,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2299,22 +2263,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2341,13 +2305,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2376,22 +2340,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2415,19 +2379,19 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2456,19 +2420,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2492,16 +2456,16 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
+        <v>7</v>
+      </c>
+      <c r="W26">
+        <v>10</v>
+      </c>
+      <c r="X26">
         <v>6</v>
-      </c>
-      <c r="W26">
-        <v>9</v>
-      </c>
-      <c r="X26">
-        <v>5</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2530,22 +2494,22 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2575,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2607,22 +2571,22 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2643,19 +2607,19 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2809,7 +2773,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -2827,7 +2791,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2868,7 +2832,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -2886,7 +2850,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2915,37 +2879,37 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S6">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2971,40 +2935,40 @@
         <v>88</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="I7">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N7">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="O7">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S7">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3030,10 +2994,10 @@
         <v>96</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3045,13 +3009,13 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3063,7 +3027,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3089,40 +3053,40 @@
         <v>96</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M9">
+        <v>98</v>
+      </c>
+      <c r="N9">
+        <v>97.5</v>
+      </c>
+      <c r="O9">
+        <v>94</v>
+      </c>
+      <c r="P9">
         <v>96</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>92</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3148,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3166,10 +3130,10 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3207,7 +3171,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3225,7 +3189,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3266,10 +3230,10 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3281,13 +3245,13 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3299,7 +3263,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3325,10 +3289,10 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3343,10 +3307,10 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3446,7 +3410,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -3464,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3502,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3517,10 +3481,10 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3535,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3564,10 +3528,10 @@
         <v>85</v>
       </c>
       <c r="I17">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3582,10 +3546,10 @@
         <v>85</v>
       </c>
       <c r="O17">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3620,10 +3584,10 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -3635,13 +3599,13 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -3653,7 +3617,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3679,7 +3643,7 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -3694,10 +3658,10 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3712,7 +3676,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3738,10 +3702,10 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I20">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -3750,16 +3714,16 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O20">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -3768,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3800,7 +3764,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -3818,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3856,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I22">
         <v>96</v>
@@ -3871,10 +3835,10 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O22">
         <v>96</v>
@@ -3889,7 +3853,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3915,13 +3879,13 @@
         <v>88</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I23">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -3930,16 +3894,16 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O23">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -3948,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4048,7 +4012,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4066,7 +4030,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4092,40 +4056,40 @@
         <v>96</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M26">
+        <v>98</v>
+      </c>
+      <c r="N26">
+        <v>92.5</v>
+      </c>
+      <c r="O26">
+        <v>86</v>
+      </c>
+      <c r="P26">
         <v>96</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>80</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S26">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4151,40 +4115,40 @@
         <v>96</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="I27">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="O27">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S27">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4210,40 +4174,40 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="I28">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M28">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N28">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="O28">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S28">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4273,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4332,28 +4296,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>25</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4367,25 +4331,25 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4396,10 +4360,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -4417,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4431,7 +4395,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -4449,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4481,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4531,7 +4495,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4563,16 +4527,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920297</v>
+        <v>22330051920412</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4586,16 +4550,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920415</v>
+        <v>22330051920298</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4609,16 +4573,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920298</v>
+        <v>22330051920397</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -4627,121 +4591,6 @@
         <v>49</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920417</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920306</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920308</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920370</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920397</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20241.xlsx
+++ b/grupos/5ASV - Estadisticos 20241.xlsx
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -2417,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2453,7 +2453,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/5ASV - Estadisticos 20241.xlsx
+++ b/grupos/5ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -59,6 +59,9 @@
     <t>AYALA LEON MARCOS</t>
   </si>
   <si>
+    <t>BAUTISTA ALVAREZ EFRAIN DE JESUS</t>
+  </si>
+  <si>
     <t>CANTE REYES TOMAS RAFAEL</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t>HERNANDEZ HERNANDEZ AARON</t>
   </si>
   <si>
+    <t>HERNANDEZ MARTINEZ GAMALIEL</t>
+  </si>
+  <si>
     <t>LIBRADO SANCHEZ LESLIE YAMILET</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
     <t>PANTOJA HERNANDEZ SANTIAGO</t>
   </si>
   <si>
+    <t>PARRA FLORES MOISES ALBERTO</t>
+  </si>
+  <si>
     <t>PEREZ ISLAS ANA LAURA</t>
   </si>
   <si>
@@ -131,6 +140,9 @@
     <t>VELAZQUEZ PAZ GUILLERMO ALEXANDER</t>
   </si>
   <si>
+    <t>VENTURA TEZOCO ZABDIEL</t>
+  </si>
+  <si>
     <t>F1</t>
   </si>
   <si>
@@ -167,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
+    <t>Castillo Cruz Carlos Samuel</t>
+  </si>
+  <si>
     <t>Ramírez Vargas Miranda Alejandra</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Castillo Cruz Carlos Samuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,31 +203,40 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
+    <t>MOISES ALBERTO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -577,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -741,19 +762,19 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -771,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -782,37 +803,37 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -821,7 +842,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -833,25 +854,25 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="U5">
         <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -859,76 +880,76 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -936,13 +957,13 @@
         <v>15</v>
       </c>
       <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
         <v>6</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -954,58 +975,58 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1013,10 +1034,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1028,52 +1049,52 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1082,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1090,76 +1111,76 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>10</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>6</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1167,55 +1188,55 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
         <v>6</v>
       </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
       <c r="G10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1224,19 +1245,19 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1244,7 +1265,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -1256,10 +1277,10 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -1268,37 +1289,37 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1307,13 +1328,13 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1321,76 +1342,76 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
       <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12">
+        <v>7</v>
+      </c>
+      <c r="K12">
+        <v>9</v>
+      </c>
+      <c r="L12">
+        <v>7</v>
+      </c>
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>8</v>
-      </c>
-      <c r="I12">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>8</v>
-      </c>
-      <c r="M12">
-        <v>10</v>
-      </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1398,25 +1419,25 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>10</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -1428,43 +1449,43 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1475,19 +1496,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1502,28 +1523,28 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1535,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1552,7 +1573,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -1564,64 +1585,64 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>9</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1629,13 +1650,13 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>10</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -1647,43 +1668,43 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>9</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -1695,7 +1716,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1709,19 +1730,19 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>9</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>9</v>
@@ -1733,49 +1754,49 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1783,73 +1804,73 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C18">
         <v>10</v>
       </c>
       <c r="D18">
+        <v>-1</v>
+      </c>
+      <c r="E18">
+        <v>-1</v>
+      </c>
+      <c r="F18">
+        <v>-1</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>-1</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>-1</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>-1</v>
+      </c>
+      <c r="M18">
+        <v>9</v>
+      </c>
+      <c r="N18">
+        <v>-1</v>
+      </c>
+      <c r="O18">
+        <v>10</v>
+      </c>
+      <c r="P18">
+        <v>-1</v>
+      </c>
+      <c r="Q18">
+        <v>-1</v>
+      </c>
+      <c r="R18">
+        <v>-1</v>
+      </c>
+      <c r="S18">
+        <v>9</v>
+      </c>
+      <c r="T18">
+        <v>-1</v>
+      </c>
+      <c r="U18">
+        <v>10</v>
+      </c>
+      <c r="V18">
         <v>5</v>
       </c>
-      <c r="E18">
-        <v>9</v>
-      </c>
-      <c r="F18">
-        <v>6</v>
-      </c>
-      <c r="G18">
-        <v>9</v>
-      </c>
-      <c r="H18">
-        <v>9</v>
-      </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18">
-        <v>9</v>
-      </c>
-      <c r="K18">
-        <v>9</v>
-      </c>
-      <c r="L18">
-        <v>9</v>
-      </c>
-      <c r="M18">
-        <v>9</v>
-      </c>
-      <c r="N18">
-        <v>-1</v>
-      </c>
-      <c r="O18">
-        <v>-1</v>
-      </c>
-      <c r="P18">
-        <v>-1</v>
-      </c>
-      <c r="Q18">
-        <v>-1</v>
-      </c>
-      <c r="R18">
-        <v>-1</v>
-      </c>
-      <c r="S18">
-        <v>-1</v>
-      </c>
-      <c r="T18">
-        <v>10</v>
-      </c>
-      <c r="U18">
-        <v>10</v>
-      </c>
-      <c r="V18">
-        <v>7</v>
-      </c>
       <c r="W18">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1860,76 +1881,76 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>8</v>
+      </c>
+      <c r="K19">
+        <v>8</v>
+      </c>
+      <c r="L19">
+        <v>9</v>
+      </c>
+      <c r="M19">
+        <v>8</v>
+      </c>
+      <c r="N19">
+        <v>8</v>
+      </c>
+      <c r="O19">
+        <v>10</v>
+      </c>
+      <c r="P19">
+        <v>5</v>
+      </c>
+      <c r="Q19">
+        <v>9</v>
+      </c>
+      <c r="R19">
+        <v>5</v>
+      </c>
+      <c r="S19">
+        <v>-1</v>
+      </c>
+      <c r="T19">
+        <v>8</v>
+      </c>
+      <c r="U19">
+        <v>10</v>
+      </c>
+      <c r="V19">
+        <v>7</v>
+      </c>
+      <c r="W19">
+        <v>9</v>
+      </c>
+      <c r="X19">
         <v>6</v>
       </c>
-      <c r="G19">
-        <v>8</v>
-      </c>
-      <c r="H19">
-        <v>10</v>
-      </c>
-      <c r="I19">
-        <v>10</v>
-      </c>
-      <c r="J19">
-        <v>8</v>
-      </c>
-      <c r="K19">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <v>9</v>
-      </c>
-      <c r="M19">
-        <v>9</v>
-      </c>
-      <c r="N19">
-        <v>-1</v>
-      </c>
-      <c r="O19">
-        <v>-1</v>
-      </c>
-      <c r="P19">
-        <v>-1</v>
-      </c>
-      <c r="Q19">
-        <v>-1</v>
-      </c>
-      <c r="R19">
-        <v>-1</v>
-      </c>
-      <c r="S19">
-        <v>-1</v>
-      </c>
-      <c r="T19">
-        <v>10</v>
-      </c>
-      <c r="U19">
-        <v>10</v>
-      </c>
-      <c r="V19">
-        <v>8</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19">
-        <v>8</v>
-      </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1937,19 +1958,19 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -1961,49 +1982,49 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>7</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2017,19 +2038,19 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>10</v>
@@ -2038,31 +2059,31 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2074,16 +2095,16 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2094,28 +2115,28 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>9</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2124,34 +2145,34 @@
         <v>7</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2160,7 +2181,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2168,73 +2189,73 @@
         <v>31</v>
       </c>
       <c r="B23">
+        <v>-1</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>-1</v>
+      </c>
+      <c r="E23">
+        <v>-1</v>
+      </c>
+      <c r="F23">
+        <v>-1</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <v>-1</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+      <c r="K23">
+        <v>-1</v>
+      </c>
+      <c r="L23">
+        <v>-1</v>
+      </c>
+      <c r="M23">
+        <v>8</v>
+      </c>
+      <c r="N23">
+        <v>-1</v>
+      </c>
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23">
+        <v>-1</v>
+      </c>
+      <c r="Q23">
+        <v>-1</v>
+      </c>
+      <c r="R23">
+        <v>-1</v>
+      </c>
+      <c r="S23">
+        <v>8</v>
+      </c>
+      <c r="T23">
+        <v>-1</v>
+      </c>
+      <c r="U23">
+        <v>10</v>
+      </c>
+      <c r="V23">
         <v>5</v>
       </c>
-      <c r="C23">
-        <v>8</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23">
-        <v>9</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23">
-        <v>7</v>
-      </c>
-      <c r="H23">
-        <v>8</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>7</v>
-      </c>
-      <c r="K23">
-        <v>9</v>
-      </c>
-      <c r="L23">
-        <v>8</v>
-      </c>
-      <c r="M23">
-        <v>8</v>
-      </c>
-      <c r="N23">
-        <v>-1</v>
-      </c>
-      <c r="O23">
-        <v>-1</v>
-      </c>
-      <c r="P23">
-        <v>-1</v>
-      </c>
-      <c r="Q23">
-        <v>-1</v>
-      </c>
-      <c r="R23">
-        <v>-1</v>
-      </c>
-      <c r="S23">
-        <v>-1</v>
-      </c>
-      <c r="T23">
-        <v>7</v>
-      </c>
-      <c r="U23">
-        <v>9</v>
-      </c>
-      <c r="V23">
-        <v>6</v>
-      </c>
       <c r="W23">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2248,16 +2269,16 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>9</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>10</v>
@@ -2269,31 +2290,31 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
       </c>
       <c r="M24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2305,13 +2326,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2322,76 +2343,76 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2399,13 +2420,13 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2414,46 +2435,46 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2462,13 +2483,13 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2476,76 +2497,76 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>10</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2553,76 +2574,384 @@
         <v>36</v>
       </c>
       <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>9</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>9</v>
+      </c>
+      <c r="J28">
+        <v>8</v>
+      </c>
+      <c r="K28">
+        <v>10</v>
+      </c>
+      <c r="L28">
+        <v>9</v>
+      </c>
+      <c r="M28">
+        <v>7</v>
+      </c>
+      <c r="N28">
+        <v>10</v>
+      </c>
+      <c r="O28">
+        <v>10</v>
+      </c>
+      <c r="P28">
+        <v>9</v>
+      </c>
+      <c r="Q28">
+        <v>10</v>
+      </c>
+      <c r="R28">
+        <v>9</v>
+      </c>
+      <c r="S28">
+        <v>-1</v>
+      </c>
+      <c r="T28">
+        <v>8</v>
+      </c>
+      <c r="U28">
+        <v>9</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>10</v>
+      </c>
+      <c r="X28">
+        <v>8</v>
+      </c>
+      <c r="Y28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
         <v>5</v>
       </c>
-      <c r="C28">
-        <v>8</v>
-      </c>
-      <c r="D28">
+      <c r="G29">
+        <v>9</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29">
+        <v>7</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="K29">
+        <v>10</v>
+      </c>
+      <c r="L29">
+        <v>7</v>
+      </c>
+      <c r="M29">
+        <v>8</v>
+      </c>
+      <c r="N29">
+        <v>7</v>
+      </c>
+      <c r="O29">
+        <v>9</v>
+      </c>
+      <c r="P29">
+        <v>7</v>
+      </c>
+      <c r="Q29">
+        <v>10</v>
+      </c>
+      <c r="R29">
+        <v>9</v>
+      </c>
+      <c r="S29">
+        <v>-1</v>
+      </c>
+      <c r="T29">
+        <v>8</v>
+      </c>
+      <c r="U29">
+        <v>9</v>
+      </c>
+      <c r="V29">
+        <v>7</v>
+      </c>
+      <c r="W29">
+        <v>10</v>
+      </c>
+      <c r="X29">
+        <v>7</v>
+      </c>
+      <c r="Y29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30">
         <v>5</v>
       </c>
-      <c r="E28">
-        <v>9</v>
-      </c>
-      <c r="F28">
+      <c r="G30">
+        <v>9</v>
+      </c>
+      <c r="H30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+      <c r="J30">
+        <v>6</v>
+      </c>
+      <c r="K30">
+        <v>10</v>
+      </c>
+      <c r="L30">
+        <v>6</v>
+      </c>
+      <c r="M30">
+        <v>9</v>
+      </c>
+      <c r="N30">
+        <v>10</v>
+      </c>
+      <c r="O30">
+        <v>10</v>
+      </c>
+      <c r="P30">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>10</v>
+      </c>
+      <c r="R30">
+        <v>9</v>
+      </c>
+      <c r="S30">
+        <v>-1</v>
+      </c>
+      <c r="T30">
+        <v>8</v>
+      </c>
+      <c r="U30">
+        <v>9</v>
+      </c>
+      <c r="V30">
+        <v>7</v>
+      </c>
+      <c r="W30">
+        <v>10</v>
+      </c>
+      <c r="X30">
+        <v>7</v>
+      </c>
+      <c r="Y30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31">
         <v>5</v>
       </c>
-      <c r="G28">
-        <v>7</v>
-      </c>
-      <c r="H28">
-        <v>7</v>
-      </c>
-      <c r="I28">
-        <v>10</v>
-      </c>
-      <c r="J28">
-        <v>7</v>
-      </c>
-      <c r="K28">
-        <v>9</v>
-      </c>
-      <c r="L28">
-        <v>8</v>
-      </c>
-      <c r="M28">
-        <v>7</v>
-      </c>
-      <c r="N28">
-        <v>-1</v>
-      </c>
-      <c r="O28">
-        <v>-1</v>
-      </c>
-      <c r="P28">
-        <v>-1</v>
-      </c>
-      <c r="Q28">
-        <v>-1</v>
-      </c>
-      <c r="R28">
-        <v>-1</v>
-      </c>
-      <c r="S28">
-        <v>-1</v>
-      </c>
-      <c r="T28">
+      <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>7</v>
+      </c>
+      <c r="H31">
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>7</v>
+      </c>
+      <c r="K31">
+        <v>9</v>
+      </c>
+      <c r="L31">
+        <v>8</v>
+      </c>
+      <c r="M31">
+        <v>7</v>
+      </c>
+      <c r="N31">
+        <v>10</v>
+      </c>
+      <c r="O31">
+        <v>10</v>
+      </c>
+      <c r="P31">
         <v>6</v>
       </c>
-      <c r="U28">
-        <v>9</v>
-      </c>
-      <c r="V28">
+      <c r="Q31">
+        <v>9</v>
+      </c>
+      <c r="R31">
+        <v>8</v>
+      </c>
+      <c r="S31">
+        <v>-1</v>
+      </c>
+      <c r="T31">
+        <v>7</v>
+      </c>
+      <c r="U31">
+        <v>9</v>
+      </c>
+      <c r="V31">
         <v>6</v>
       </c>
-      <c r="W28">
-        <v>9</v>
-      </c>
-      <c r="X28">
-        <v>7</v>
-      </c>
-      <c r="Y28">
-        <v>7</v>
+      <c r="W31">
+        <v>9</v>
+      </c>
+      <c r="X31">
+        <v>7</v>
+      </c>
+      <c r="Y31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32">
+        <v>-1</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>-1</v>
+      </c>
+      <c r="E32">
+        <v>-1</v>
+      </c>
+      <c r="F32">
+        <v>-1</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>-1</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="J32">
+        <v>-1</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
+        <v>-1</v>
+      </c>
+      <c r="M32">
+        <v>10</v>
+      </c>
+      <c r="N32">
+        <v>-1</v>
+      </c>
+      <c r="O32">
+        <v>10</v>
+      </c>
+      <c r="P32">
+        <v>-1</v>
+      </c>
+      <c r="Q32">
+        <v>-1</v>
+      </c>
+      <c r="R32">
+        <v>-1</v>
+      </c>
+      <c r="S32">
+        <v>10</v>
+      </c>
+      <c r="T32">
+        <v>-1</v>
+      </c>
+      <c r="U32">
+        <v>10</v>
+      </c>
+      <c r="V32">
+        <v>5</v>
+      </c>
+      <c r="W32">
+        <v>-1</v>
+      </c>
+      <c r="X32">
+        <v>-1</v>
+      </c>
+      <c r="Y32">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2638,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2647,7 +2976,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2655,7 +2984,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -2663,7 +2992,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -2779,7 +3108,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -2791,7 +3120,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>98</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2799,58 +3128,58 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2861,7 +3190,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -2879,37 +3208,37 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>96</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>97.5</v>
       </c>
-      <c r="M6">
-        <v>94</v>
-      </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
-        <v>88</v>
-      </c>
       <c r="P6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2917,58 +3246,58 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C7">
+        <v>96</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>88</v>
       </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>77.5</v>
-      </c>
-      <c r="I7">
-        <v>84</v>
-      </c>
       <c r="J7">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>92.5</v>
+        <v>97.5</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N7">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="P7">
-        <v>92</v>
+        <v>97.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S7">
-        <v>84</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2976,10 +3305,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -2991,43 +3320,43 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H8">
-        <v>97.5</v>
+        <v>77.5</v>
       </c>
       <c r="I8">
+        <v>84</v>
+      </c>
+      <c r="J8">
         <v>92</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M8">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="N8">
-        <v>97.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O8">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S8">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3038,7 +3367,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -3056,37 +3385,37 @@
         <v>97.5</v>
       </c>
       <c r="I9">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J9">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>98</v>
       </c>
       <c r="N9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O9">
-        <v>94</v>
+        <v>87.5</v>
       </c>
       <c r="P9">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>98</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3097,7 +3426,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -3109,43 +3438,43 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H10">
-        <v>87.5</v>
+        <v>97.5</v>
       </c>
       <c r="I10">
+        <v>94</v>
+      </c>
+      <c r="J10">
         <v>96</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N10">
-        <v>87.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O10">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3171,10 +3500,10 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>97.5</v>
+        <v>87.5</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3189,10 +3518,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3204,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3230,10 +3559,10 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>87.5</v>
+        <v>97.5</v>
       </c>
       <c r="I12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3245,13 +3574,13 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>87.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3263,7 +3592,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>98</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3289,10 +3618,10 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>97.5</v>
+        <v>87.5</v>
       </c>
       <c r="I13">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3304,13 +3633,13 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N13">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="O13">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3322,7 +3651,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3348,10 +3677,10 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3366,13 +3695,13 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3381,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3392,7 +3721,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -3410,7 +3739,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -3425,10 +3754,10 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O15">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3440,7 +3769,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3451,7 +3780,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -3466,10 +3795,10 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3481,13 +3810,13 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3499,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>98</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3507,10 +3836,10 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -3522,16 +3851,16 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>97.5</v>
       </c>
       <c r="I17">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3540,16 +3869,16 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N17">
-        <v>85</v>
+        <v>95.3</v>
       </c>
       <c r="O17">
-        <v>86</v>
+        <v>97.5</v>
       </c>
       <c r="P17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3558,7 +3887,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>92</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3566,58 +3895,58 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3625,10 +3954,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -3643,13 +3972,13 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>97.5</v>
+        <v>85</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -3658,25 +3987,25 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N19">
-        <v>97.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>86.3</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S19">
-        <v>96</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3684,29 +4013,29 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20">
+        <v>92</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>92</v>
+      </c>
+      <c r="H20">
+        <v>97.5</v>
+      </c>
+      <c r="I20">
         <v>96</v>
       </c>
-      <c r="D20">
-        <v>100</v>
-      </c>
-      <c r="E20">
-        <v>100</v>
-      </c>
-      <c r="F20">
-        <v>100</v>
-      </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20">
-        <v>92.5</v>
-      </c>
-      <c r="I20">
-        <v>98</v>
-      </c>
       <c r="J20">
         <v>100</v>
       </c>
@@ -3714,16 +4043,16 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N20">
-        <v>92.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O20">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -3732,10 +4061,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3746,43 +4075,43 @@
         <v>100</v>
       </c>
       <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>92</v>
+      </c>
+      <c r="H21">
+        <v>97.5</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
         <v>96</v>
       </c>
-      <c r="D21">
-        <v>100</v>
-      </c>
-      <c r="E21">
-        <v>100</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>100</v>
-      </c>
-      <c r="H21">
-        <v>100</v>
-      </c>
-      <c r="I21">
-        <v>98</v>
-      </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3794,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3802,7 +4131,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>96</v>
@@ -3820,40 +4149,40 @@
         <v>100</v>
       </c>
       <c r="H22">
+        <v>92.5</v>
+      </c>
+      <c r="I22">
+        <v>98</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>97.5</v>
       </c>
-      <c r="I22">
-        <v>96</v>
-      </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="O22">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S22">
-        <v>98</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3861,58 +4190,58 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N23">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3923,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -3941,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -3959,7 +4288,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -3971,7 +4300,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3979,10 +4308,10 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C25">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -3997,10 +4326,10 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I25">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4015,22 +4344,22 @@
         <v>98</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="O25">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S25">
-        <v>98</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4041,7 +4370,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -4053,13 +4382,13 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H26">
-        <v>92.5</v>
+        <v>97.5</v>
       </c>
       <c r="I26">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J26">
         <v>96</v>
@@ -4068,28 +4397,28 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N26">
-        <v>92.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O26">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P26">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>98</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4100,7 +4429,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -4112,43 +4441,43 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>98</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4156,58 +4485,294 @@
         <v>36</v>
       </c>
       <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>92</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+      <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>92</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>98</v>
+      </c>
+      <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
+        <v>95</v>
+      </c>
+      <c r="P28">
+        <v>98.8</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
         <v>80</v>
       </c>
-      <c r="C28">
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>96</v>
+      </c>
+      <c r="H29">
+        <v>92.5</v>
+      </c>
+      <c r="I29">
+        <v>86</v>
+      </c>
+      <c r="J29">
+        <v>96</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>92.5</v>
+      </c>
+      <c r="M29">
+        <v>98</v>
+      </c>
+      <c r="N29">
+        <v>95.3</v>
+      </c>
+      <c r="O29">
+        <v>86.3</v>
+      </c>
+      <c r="P29">
+        <v>97.5</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>95.3</v>
+      </c>
+      <c r="S29">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30">
+        <v>92</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>96</v>
+      </c>
+      <c r="H30">
+        <v>77.5</v>
+      </c>
+      <c r="I30">
+        <v>82</v>
+      </c>
+      <c r="J30">
+        <v>94</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>95</v>
+      </c>
+      <c r="M30">
+        <v>98</v>
+      </c>
+      <c r="N30">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="O30">
+        <v>81.3</v>
+      </c>
+      <c r="P30">
+        <v>96.3</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="S30">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31">
         <v>80</v>
       </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
-      <c r="E28">
-        <v>100</v>
-      </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
-      <c r="G28">
+      <c r="C31">
+        <v>80</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
         <v>92</v>
       </c>
-      <c r="H28">
+      <c r="H31">
         <v>87.5</v>
       </c>
-      <c r="I28">
+      <c r="I31">
         <v>86</v>
       </c>
-      <c r="J28">
+      <c r="J31">
         <v>94</v>
       </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>92.5</v>
       </c>
-      <c r="M28">
+      <c r="M31">
         <v>94</v>
       </c>
-      <c r="N28">
-        <v>87.5</v>
-      </c>
-      <c r="O28">
-        <v>86</v>
-      </c>
-      <c r="P28">
-        <v>94</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
-        <v>92.5</v>
-      </c>
-      <c r="S28">
-        <v>94</v>
+      <c r="N31">
+        <v>92.2</v>
+      </c>
+      <c r="O31">
+        <v>83.8</v>
+      </c>
+      <c r="P31">
+        <v>95</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>95.3</v>
+      </c>
+      <c r="S31">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4235,89 +4800,89 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2">
+        <v>29</v>
+      </c>
+      <c r="D2">
         <v>25</v>
       </c>
-      <c r="D2">
-        <v>22</v>
-      </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>88</v>
+        <v>86.2</v>
       </c>
       <c r="G2" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4328,13 +4893,13 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -4343,30 +4908,30 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>25</v>
@@ -4375,33 +4940,33 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4413,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4424,16 +4989,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4445,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4461,7 +5026,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4470,22 +5035,342 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920291</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920305</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>22330051920305</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>22330051920305</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>22330051920305</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>22330051920309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>22330051920309</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>22330051920309</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>22330051920309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>22330051920315</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>22330051920315</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>22330051920315</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>22330051920315</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4495,7 +5380,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4504,22 +5389,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4527,45 +5412,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920412</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920298</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4573,25 +5458,324 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920397</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920305</v>
+      </c>
+      <c r="B6" t="s">
         <v>62</v>
       </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4">
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
         <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920305</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920305</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920305</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920309</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920309</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920315</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920315</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920315</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920315</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ASV - Estadisticos 20241.xlsx
+++ b/grupos/5ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="61">
   <si>
     <t>Materia</t>
   </si>
@@ -179,6 +179,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -188,9 +191,6 @@
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -201,42 +201,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -777,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -803,73 +767,73 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -931,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1008,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1085,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1103,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1162,7 +1126,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1239,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1316,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1334,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1393,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1470,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1547,7 +1511,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1624,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1642,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1701,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1719,7 +1683,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1778,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1804,73 +1768,73 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>10</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1932,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -1950,7 +1914,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2009,7 +1973,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2086,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2104,7 +2068,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2163,7 +2127,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2181,7 +2145,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2189,73 +2153,73 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2317,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2394,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2471,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2489,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2548,7 +2512,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2625,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2702,7 +2666,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2720,7 +2684,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2779,7 +2743,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -2797,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2856,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2874,7 +2838,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2882,73 +2846,73 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3120,7 +3084,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>65.3</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3128,58 +3092,58 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3238,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>64</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3297,7 +3261,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S7">
-        <v>62.7</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3356,7 +3320,7 @@
         <v>93.8</v>
       </c>
       <c r="S8">
-        <v>56</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3415,7 +3379,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3474,7 +3438,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S10">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3533,7 +3497,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3592,7 +3556,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3651,7 +3615,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3710,7 +3674,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>66.7</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3769,7 +3733,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>66.7</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3828,7 +3792,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>66.7</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3887,7 +3851,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3895,58 +3859,58 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4005,7 +3969,7 @@
         <v>95.3</v>
       </c>
       <c r="S19">
-        <v>61.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4064,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>64</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4123,7 +4087,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>64</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4182,7 +4146,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S22">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4190,58 +4154,58 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4300,7 +4264,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>66.7</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4359,7 +4323,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S25">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4418,7 +4382,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>61.3</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4477,7 +4441,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4536,7 +4500,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>65.3</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4595,7 +4559,7 @@
         <v>95.3</v>
       </c>
       <c r="S29">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4654,7 +4618,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S30">
-        <v>65.3</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4713,7 +4677,7 @@
         <v>95.3</v>
       </c>
       <c r="S31">
-        <v>62.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4721,58 +4685,58 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
   </sheetData>
@@ -4829,7 +4793,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -4838,30 +4802,30 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -4870,19 +4834,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4893,39 +4857,39 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>29</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -4934,33 +4898,33 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>29</v>
@@ -4978,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4989,10 +4953,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>29</v>
@@ -5010,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5026,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5053,326 +5017,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920291</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920305</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920305</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920305</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920305</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920309</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920309</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920315</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920315</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920315</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920315</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5380,7 +5024,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5410,374 +5054,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920291</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920305</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920305</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920305</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920305</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920309</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920309</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920315</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920315</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920315</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920315</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
